--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\DE_auswendig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57D7BCA-757B-4ECA-BEDE-5B50DA42E3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C905AE1A-56C7-49A5-A956-D481CBD31BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="84">
   <si>
     <t>Isla</t>
   </si>
@@ -256,12 +256,111 @@
   <si>
     <t>Justificar un retraso</t>
   </si>
+  <si>
+    <t>Freizeit und Hobby</t>
+  </si>
+  <si>
+    <t>FH_1</t>
+  </si>
+  <si>
+    <t>Endlich Wochenende! Ich freue mich schon die ganze Woche darauf.
+Normalerweise schlafe ich am Samstag erstmal richtig aus.
+Dann treffe ich mich meistens mit Freunden zum Brunchen.
+Danach haben wir oft Lust, etwas zu unternehmen.
+Manchmal gehen wir spazieren, manchmal ins Kino.
+Es kommt ganz darauf an, wie das Wetter ist.
+Bei schönem Wetter zieht es uns nach draußen.
+Bei Regen machen wir es uns lieber gemütlich und schauen Serien.
+Am Sonntagabend bereite ich mich schon auf die neue Woche vor.
+Aber vorher genieße ich noch die freie Zeit!</t>
+  </si>
+  <si>
+    <t>Mi rutina de fin de semana</t>
+  </si>
+  <si>
+    <t>¡Por fin fin de semana! Llevo toda la semana esperándolo.
+Normalmente los sábados primero duermo bien hasta tarde.
+Luego suelo quedar con amigos para hacer un brunch.
+Después solemos tener ganas de hacer algo.
+A veces vamos a pasear, a veces al cine.
+Depende totalmente de cómo esté el tiempo.
+Cuando hace buen tiempo nos llama el aire libre.
+Cuando llueve preferimos ponernos cómodos y ver series.
+El domingo por la noche ya me preparo para la nueva semana.
+¡Pero antes disfruto aún del tiempo libre!</t>
+  </si>
+  <si>
+    <t>Mis hobbies y pasiones</t>
+  </si>
+  <si>
+    <t>Ich habe eigentlich ziemlich viele Hobbies.
+Am liebsten verbringe ich meine Zeit mit Lesen.
+Ich verschlinge regelrecht Bücher, vor allem Krimis.
+Außerdem spiele ich seit meiner Kindheit Klavier.
+Das hilft mir total beim Abschalten nach der Arbeit.
+Zweimal die Woche gehe ich auch ins Fitnessstudio.
+Ehrlich gesagt, manchmal überwinde ich mich nur schwer.
+Aber danach fühle ich mich immer viel besser.
+Am Wochenende unternehme ich gerne längere Radtouren.
+So kann ich den Kopf freibekommen und Energie tanken.
+Ohne meine Hobbies würde mir definitiv etwas fehlen!</t>
+  </si>
+  <si>
+    <t>La verdad es que tengo bastantes hobbies.
+Lo que más me gusta es pasar mi tiempo leyendo.
+Devoro literalmente los libros, sobre todo novelas policíacas.
+Además toco el piano desde que era niño/a.
+Eso me ayuda muchísimo a desconectar después del trabajo.
+Dos veces por semana también voy al gimnasio.
+Sinceramente, a veces me cuesta horrores motivarme.
+Pero después siempre me siento mucho mejor.
+Los fines de semana me gusta hacer rutas largas en bici.
+Así puedo despejar la mente y recargar energías.
+¡Sin mis hobbies definitivamente me faltaría algo!</t>
+  </si>
+  <si>
+    <t>Planes para las próximas vacaciones</t>
+  </si>
+  <si>
+    <t>Ich plane gerade meinen nächsten Urlaub.
+Dieses Mal möchte ich etwas ganz anderes machen.
+Normalerweise liege ich nur faul am Strand herum.
+Aber diesmal habe ich Lust auf mehr Abenteuer.
+Ich überlege, eine Wanderreise in den Bergen zu machen.
+Tagsüber wandern, abends in gemütlichen Hütten übernachten.
+Das klingt nach der perfekten Mischung aus Sport und Entspannung.
+Oder vielleicht sollte ich doch lieber eine Städtereise buchen?
+Museen besuchen, die lokale Küche probieren, durch Gassen schlendern...
+Ach, ich kann mich einfach nicht entscheiden!
+Eines steht fest: Ich brauche dringend eine Auszeit vom Alltag.
+Hauptsache weg von hier und mal richtig abschalten!</t>
+  </si>
+  <si>
+    <t>Estoy planeando mis próximas vacaciones.
+Esta vez quiero hacer algo completamente diferente.
+Normalmente solo estoy tirado/a en la playa sin hacer nada.
+Pero esta vez tengo ganas de más aventura.
+Estoy pensando en hacer un viaje de senderismo por las montañas.
+De día caminar, por la noche dormir en refugios acogedores.
+Suena como la mezcla perfecta de deporte y relax.
+¿O quizás debería reservar mejor un viaje urbano?
+Visitar museos, probar la gastronomía local, pasear por callejuelas...
+¡Ay, es que no puedo decidirme!
+Una cosa está clara: necesito urgentemente un descanso de la rutina.
+¡Lo principal es salir de aquí y desconectar de verdad!</t>
+  </si>
+  <si>
+    <t>FH_2</t>
+  </si>
+  <si>
+    <t>FH_3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +378,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -614,7 +706,7 @@
   <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
     <col min="2" max="2" width="80.90625" customWidth="1"/>
     <col min="3" max="3" width="78.453125" customWidth="1"/>
     <col min="5" max="5" width="61.26953125" customWidth="1"/>
@@ -926,28 +1018,58 @@
       </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="2"/>
+    <row r="18" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="2"/>
+    <row r="19" spans="1:6" ht="143.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="2"/>
+    <row r="20" spans="1:6" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -955,7 +1077,7 @@
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="2"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -963,7 +1085,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="2"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -971,7 +1093,7 @@
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="2"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1115,7 +1237,7 @@
       <c r="D46" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\DE_auswendig\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C905AE1A-56C7-49A5-A956-D481CBD31BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB260E87-835D-432B-A741-F4110565D45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
   <si>
     <t>Isla</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>FH_3</t>
+  </si>
+  <si>
+    <t>Dominio</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -423,9 +426,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -704,15 +713,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="80.90625" customWidth="1"/>
-    <col min="3" max="3" width="78.453125" customWidth="1"/>
-    <col min="5" max="5" width="61.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.4609375" customWidth="1"/>
+    <col min="2" max="2" width="80.921875" customWidth="1"/>
+    <col min="3" max="3" width="78.4609375" customWidth="1"/>
+    <col min="5" max="5" width="61.23046875" customWidth="1"/>
+    <col min="6" max="6" width="7.23046875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -728,9 +738,11 @@
       <c r="E1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="52" x14ac:dyDescent="0.35">
+      <c r="F1" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="51.45" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -746,9 +758,11 @@
       <c r="E2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -764,9 +778,11 @@
       <c r="E3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -782,9 +798,11 @@
       <c r="E4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="39" x14ac:dyDescent="0.35">
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -800,9 +818,11 @@
       <c r="E5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -818,9 +838,11 @@
       <c r="E6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -836,9 +858,11 @@
       <c r="E7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -854,9 +878,11 @@
       <c r="E8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -872,9 +898,11 @@
       <c r="E9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -890,9 +918,11 @@
       <c r="E10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
@@ -908,9 +938,11 @@
       <c r="E11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -926,9 +958,11 @@
       <c r="E12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -944,9 +978,11 @@
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -962,9 +998,11 @@
       <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -980,9 +1018,11 @@
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -998,9 +1038,11 @@
       <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1016,9 +1058,11 @@
       <c r="E17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="129" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
@@ -1034,9 +1078,11 @@
       <c r="E18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="143.5" x14ac:dyDescent="0.35">
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="141.9" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
@@ -1052,9 +1098,11 @@
       <c r="E19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="154.75" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1070,167 +1118,169 @@
       <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="3"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="4"/>
       <c r="B33" s="1"/>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="4"/>
       <c r="B34" s="1"/>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="4"/>
       <c r="B35" s="1"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="4"/>
       <c r="B36" s="1"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
       <c r="B37" s="1"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="4"/>
       <c r="B38" s="1"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="4"/>
       <c r="B39" s="1"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="4"/>
       <c r="B40" s="1"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="4"/>
       <c r="B41" s="1"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
       <c r="B42" s="1"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="4"/>
       <c r="B43" s="1"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="4"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" s="4"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB260E87-835D-432B-A741-F4110565D45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF091D7D-450C-4277-876E-2CA4E0CD9CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>Isla</t>
   </si>
@@ -357,6 +357,144 @@
   </si>
   <si>
     <t>Dominio</t>
+  </si>
+  <si>
+    <t>Bewegung</t>
+  </si>
+  <si>
+    <t>Movimiento (Cocina / Convivencia)</t>
+  </si>
+  <si>
+    <t>So, ich fange jetzt mit dem Kochen an.
+Kannst du mir die große Schüssel da oben rausholen?
+Die steht ganz hinten im Schrank drin.
+Ah, perfekt, danke! Stell sie einfach hier hin, wenn du willst.
+Weißt du was, hol doch auch gleich die Gewürze runter, die brauch ich sowieso.
+Genau, die da. Keine Sorge, ich stell sie nachher wieder rein.
+Ach, und nimm bitte auch die Milch aus dem Kühlschrank raus.
+Die kannst du direkt hier hinstellen, dann hab ich alles griffbereit.
+Moment mal... die Kiste mit dem Gemüse stört da total.
+Kannst du die mal ein bisschen zur Seite schieben?
+Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Schau mal, ob etwas schlecht geworden ist, und wirf es direkt weg, wenn du schon dabei bist. Unser Kühlschrank ist nämlich total vollgestopft!
+Super, so hab ich viel mehr Platz.
+Ich geh ganz kurz rüber zum Nachbarn, der wollte mir noch Eier vorbeibringen.
+Bin in zwei Minuten wieder da, ja?
+So, da bin ich wieder. Wo soll ich die Eier hinlegen? Hast du den letzten Karton weggeworfen? Ah, ich seh ihn schon, der stand genau hinter der Tupperdose mit den Makkaroni.
+Reichst du mir mal eben das Salz rüber? Danke dir!
+So, jetzt nehm ich das Fleisch raus und brate es direkt in der Pfanne an.
+Mmm, riecht schon gut, findest du nicht? Heute lassen wir es uns richtig gut schmecken!</t>
+  </si>
+  <si>
+    <t>Bueno, me voy a poner a cocinar ahora mismo.
+¿Puedes sacar el bol grande del armario de ahí arriba?
+Está justo al fondo.
+Ah, perfecto, ¡gracias! Déjalo aquí si quieres.
+Oye, ya que estás, baja también las especias, que las voy a necesitar de todas formas.
+Esas, sí. Luego no te preocupes que las vuelvo a dejar en su sitio.
+Ah, y saca también la leche de la nevera, por favor.
+Puedes ponerla directamente aquí, así tengo todo a mano.
+Espera un momento... esa caja con las verduras estorba ahí un montón.
+¿Puedes apartarla un poco? Casi mejor que saques las verduras y las coloques en la nevera en los cajones de abajo. Mira a ver si se ha puesto algo malo y lo tiras ya que estás. Es que tenemos la nevera a reventar.
+Buenos pues genial, así tengo mucho más espacio.
+Voy un segundo a casa del vecino, que me iba a traer huevos.
+Vuelvo en dos minutos, ¿vale?
+Ya está, ya estoy aquí. ¿Dónde guardo los huevos? ¿Tiraste el último cartón? Ah, ya lo veo, estaba justo detrás del táper de macarrones.
+¿Me pasas la sal un momento? ¡Gracias!
+Bueno, ahora saco la carne y la frío directamente en la sartén.
+Mmm, huele bien ya, ¿no te parece? ¡Hoy vamos a comer de lo lindo!</t>
+  </si>
+  <si>
+    <t>Bueno, hoy por fin voy a ordenar el salón.
+Estos periódicos definitivamente los voy a tirar, que solo molestan. Además, solo acumulan polvo.
+Los saco ahora mismo al papel viejo. ¿Te acuerdas de qué día se podían bajar a la calle?
+Ay madre, el cojín está otra vez tirado en el suelo. Estoy harto de recogerlo todos los días.
+¿Puedes recogerlo un momento y ponerlo de nuevo en el sofá?
+Gracias. Y por cierto, ¿dónde está el mando a distancia?
+¡Es que siempre se esconde! ¿Se habrá metido debajo del sofá como la última vez?
+Ah, ahí está, debajo de la mesa, por supuesto. Por cierto, hay que limpiar a fondo porque está lleno de migas, porquería y piezas de juguetes de la niña.
+Lo dejo aquí en la mesita, así sabemos todos dónde buscarlo.
+Hmm, la planta de allí tiene pinta de estar un poco triste y seca.
+Necesita más luz y agua, sin duda.
+La pongo junto a la ventana, a ver si eso ayuda.
+Sí, así ya está mejor.
+Ay, pero si la manta está medio caída del sillón.
+Espera, la coloco bien encima rápido, si no se va a caer del todo.
+Y los libros... pero si se están amontonando otra vez por todas partes.
+Tendría que volver a meterlos en la estantería y colocarlos bien.
+¡Ya está! Ahora se ve mucho más ordenado, ¿no crees?</t>
+  </si>
+  <si>
+    <t>So, ich räume heute endlich mal das Wohnzimmer auf.
+Die Zeitungen da können definitiv weg, die stören nur. Außerdem sammeln sie nur Staub an.
+Ich bringe sie gleich raus zum Altpapier. Weißt du noch, an welchem Tag man sie auf die Straße stellen darf?
+Ach du liebe Zeit, das Kissen liegt schon wieder auf dem Boden rum. Ich habe es satt, das jeden Tag aufzuheben.
+Kannst du es kurz aufheben und zurück aufs Sofa legen?
+Danke. Und übrigens, wo ist eigentlich die Fernbedienung schon wieder?
+Die versteckt sich doch jedes Mal! Hat sie sich vielleicht wieder unter das Sofa geschlichen, so wie letztes Mal?
+Ah, da liegt sie ja, unter dem Tisch natürlich. Übrigens müssen wir hier mal gründlich sauber machen, es liegt alles voll mit Krümeln, Dreck und Spielzeugteilen von der Kleinen.
+Ich lege sie jetzt hier hin auf den Couchtisch, dann wissen wir alle, wo wir sie suchen müssen.
+Hmm, die Pflanze da drüben sieht ein bisschen traurig und trocken aus.
+Die braucht definitiv mehr Licht und Wasser.
+Ich stelle sie mal rüber ans Fenster, mal sehen, ob das hilft.
+Ja, so ist schon besser.
+Oh Mann, die Decke hängt ja halb runter vom Sessel.
+Warte, ich hänge sie schnell richtig drüber, sonst rutscht sie gleich ganz runter.
+Und die Bücher... die stapeln sich ja schon wieder überall.
+Die sollte ich wirklich mal wieder ins Regal reinräumen und ordentlich hinstellen.
+So! Jetzt sieht's schon viel ordentlicher aus, oder?</t>
+  </si>
+  <si>
+    <t>Bewegung_1</t>
+  </si>
+  <si>
+    <t>Bewegung_2</t>
+  </si>
+  <si>
+    <t>Bewegung_3</t>
+  </si>
+  <si>
+    <t>Ich geh jetzt kurz runter zum Briefkasten.
+Kommst du mit oder bleibst du lieber hier oben?
+Ach komm schon, geh doch mit runter!
+Dann können wir auch gleich noch rüber zum Kiosk gehen.
+Wir brauchen nämlich noch Brot für morgen früh.
+Und ich wollte mir sowieso noch die Zeitung holen.
+Ach weißt du was, auf dem Rückweg gehen wir noch schnell beim Bäcker vorbei.
+Der liegt ja eh auf dem Weg.
+Moment, nimm doch bitte die Tasche mit, dann können wir alles da reinpacken.
+Gut, so passt's. Ich schließ jetzt ab und dann gehen wir zu Fuß runter, weil der Aufzug nicht funktioniert.
+Achtung, pass auf! Die Treppe ist heute ein bisschen rutschig. Die haben bestimmt gerade gewischt.
+Halt dich lieber am Geländer fest, nicht dass du noch stürzt.
+So, unten angekommen. Lass uns erst mal rüber zur Post gehen.
+Ich muss nämlich noch ein Paket abholen.
+Danach laufen wir am besten den linken Weg entlang, der ist kürzer.
+Kennst du den? Nein? Ich zeig's dir.
+So, alles erledigt! Jetzt können wir wieder hoch nach Hause gehen und die Sachen abstellen.</t>
+  </si>
+  <si>
+    <t>Movimiento (Calle / Recados)</t>
+  </si>
+  <si>
+    <t>Bajo un momento al buzón.
+¿Vienes conmigo o prefieres quedarte aquí arriba?
+¡Venga va, baja conmigo!
+Así de paso podemos ir también al quiosco.
+Además es que todavía necesitamos pan para mañana por la mañana.
+Y también es que quería comprar el periódico de todas formas.
+Oye, ¿sabes qué?, de vuelta pasamos un momento por la panadería.
+De todas formas nos pilla de camino.
+Espera, coge la bolsa por favor, así podemos meter todo ahí.
+Bien, así vale. Cierro con llave y bajamos andando que el ascensor no va.
+¡Cuidado, ojo! La escalera hoy resbala un poco. La han debido de fregar.
+Mejor agárrate a la barandilla, no te vayas a caer.
+Ya está, ya estamos abajo. Vamos primero a correos.
+Es que tengo que recoger un paquete.
+Después lo mejor es que vayamos por el camino de la izquierda, que es el camino más corto.
+¿Lo conoces? ¿No? Ah pues te lo enseño.
+¡Bueno, listo! Ahora ya podemos volver a subir a casa y a dejar las cosas.</t>
+  </si>
+  <si>
+    <t>Movimiento (Salón / Limpieza)</t>
   </si>
 </sst>
 </file>
@@ -434,7 +572,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,16 +851,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.4609375" customWidth="1"/>
-    <col min="2" max="2" width="80.921875" customWidth="1"/>
-    <col min="3" max="3" width="78.4609375" customWidth="1"/>
-    <col min="5" max="5" width="61.23046875" customWidth="1"/>
-    <col min="6" max="6" width="7.23046875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="80.90625" customWidth="1"/>
+    <col min="3" max="3" width="78.453125" customWidth="1"/>
+    <col min="5" max="5" width="33.81640625" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -742,7 +880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="51.45" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="52" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -762,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -782,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -802,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="39" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -822,7 +960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -842,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -862,7 +1000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -882,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -902,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -922,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
@@ -942,7 +1080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -962,7 +1100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -982,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -1002,7 +1140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1022,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -1042,7 +1180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1062,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="129" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
@@ -1082,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="141.9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="143.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
@@ -1102,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="154.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="156.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1122,31 +1260,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="4"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="4"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="273.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3"/>
@@ -1154,133 +1328,133 @@
       <c r="E24" s="2"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="1"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="1"/>
       <c r="C31" s="3"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="1"/>
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="1"/>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="1"/>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="1"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="1"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="1"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="1"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="1"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="1"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="1"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="1"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="1"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF091D7D-450C-4277-876E-2CA4E0CD9CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C593BE-6808-4E3E-ADD8-7247E7CF8FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="123">
   <si>
     <t>Isla</t>
   </si>
@@ -496,12 +496,287 @@
   <si>
     <t>Movimiento (Salón / Limpieza)</t>
   </si>
+  <si>
+    <t>Holzbau</t>
+  </si>
+  <si>
+    <t>Holzbau_1</t>
+  </si>
+  <si>
+    <t>Ich arbeite gerade an einem Holzbauprojekt.
+Dabei geht es um Verbindungen zwischen massiven Holzelementen.
+Wir verwenden Keile aus Buchenholz, um die Module zusammenzuhalten.
+Die Keile müssen in Richtung der Schubkraft arbeiten, nicht senkrecht dazu.
+Sonst entsteht nur Reibung, aber keine richtige Verankerung.
+Das Problem bei Holz ist immer die Zugspannung quer zur Faser.
+Die muss man unbedingt vermeiden, sonst reißt das Holz auf.
+Stattdessen sollte die Belastung eher als Druckspannung quer zur Faser wirken.
+Das verträgt Holz viel besser.
+Die Keile sollten eine sanfte Neigung haben, etwa eins zu zehn.
+So vermeidet man, dass die Fasern aufgespalten werden.
+Außerdem brauchen wir eine Art Verzahnung oder Passung zwischen den Teilen.
+Nur durch Reibung allein wird die Verbindung nicht steif genug.
+Am besten ist es, wenn man die Keile nachstellen kann.
+Denn Holz arbeitet, setzt sich und die Verbindung lockert sich mit der Zeit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estoy trabajando ahora en un proyecto de construcción en madera.
+Se trata de conexiones entre elementos macizos de madera.
+Utilizamos cuñas de madera de haya para unir los módulos.
+Las cuñas tienen que trabajar en dirección del cortante, no perpendicular a él.
+Si no, solo se genera fricción, pero no un anclaje real.
+El problema con la madera es siempre la tracción perpendicular a la fibra.
+Hay que evitarla a toda costa, si no la madera se raja.
+En cambio, la carga debería actuar más bien como compresión perpendicular a la fibra.
+Eso lo tolera mucho mejor la madera.
+Las cuñas deberían tener una inclinación suave, aproximadamente uno a diez.
+Así se evita que las fibras se partan.
+Además necesitamos algún tipo de llave o encaje entre las piezas.
+Solo con fricción la unión no será suficientemente rígida.
+Lo mejor es que se puedan reajustar las cuñas.
+Porque la madera trabaja, se asienta y la conexión se afloja con el tiempo.
+</t>
+  </si>
+  <si>
+    <t>Holzbau_2</t>
+  </si>
+  <si>
+    <t>Holzbau_3</t>
+  </si>
+  <si>
+    <t>Sobre las uniones y las cuñas</t>
+  </si>
+  <si>
+    <t>El comportamiento estructural del muro</t>
+  </si>
+  <si>
+    <t>Das System funktioniert eigentlich wie aufeinandergepresste Bausteine.
+Jedes Modul für sich ist relativ schmal, aber mit quadratischer Basis.
+Das ist wichtig, damit sie nicht so leicht kippen können.
+Die Keile zwischen den Modulen beseitigen das Spiel und zwingen sie zum Kontakt.
+Dadurch entsteht eine Art Zusammenwirken, fast wie bei einem Verbundträger.
+Aber Achtung: die Verbindung ist nicht starr wie bei einem Rahmen.
+Sie verhält sich eher nachgiebig, dämpft Bewegungen ab.
+Das Ganze ist kein Diaphragma im klassischen Sinne.
+Es ist eher ein halbsteifes, dissipatives System.
+Bei Wind versuchen die einzelnen Module seitlich zu verrutschen.
+Die horizontalen Keile blockieren genau diese Bewegung direkt.
+Vertikale Keile würden dagegen nur den Reibungswiderstand erhöhen.
+Sie arbeiten nicht in Richtung der Belastung, deshalb sind sie weniger wirksam.
+Ich rechne damit, dass sich das System in den ersten Monaten etwas setzt.
+Dann muss man die Keile nachziehen, sonst verlieren sie ihre Wirkung.</t>
+  </si>
+  <si>
+    <t>El sistema funciona básicamente como bloques comprimidos entre sí.El sistema funciona básicamente como bloques comprimidos entre sí.
+Cada módulo por sí solo es relativamente estrecho, pero con base cuadrada.
+Eso es importante para que no puedan volcar tan fácilmente.
+Las cuñas entre los módulos eliminan el juego y los fuerzan al contacto.
+De esa manera se genera una especie de colaboración, casi como en una viga compuesta.
+Pero ojo: la conexión no es rígida como en un pórtico.
+Se comporta más bien de forma flexible, amortiguando movimientos.
+El conjunto no es un diafragma en el sentido clásico.
+Es más bien un sistema semirrígido y disipativo.
+Con viento, los módulos individuales intentan deslizarse lateralmente.
+Las cuñas horizontales bloquean exactamente ese movimiento directamente.
+Las cuñas verticales en cambio solo aumentarían la resistencia por fricción.
+No trabajan en dirección de la carga, por eso son menos efectivas.
+Calculo que el sistema se asentará un poco en los primeros meses.
+Entonces habrá que reajustar las cuñas, si no pierden su efecto.</t>
+  </si>
+  <si>
+    <t>Los modos de fallo y el diseño correcto</t>
+  </si>
+  <si>
+    <t>Bei Holzkonstruktionen muss man immer an die typischen Versagensmechanismen denken.
+Holz verträgt Druck parallel zur Faser ausgezeichnet.
+Auch Druck quer zur Faser geht halbwegs, da gibt es Eindrückung, aber keinen Bruch.
+Kritisch wird es bei Zug quer zur Faser.
+Das ist der klassische Fall: "das Holz hat sich geöffnet", also gespalten.
+Deshalb würde ich niemals Keile verwenden, die die senkrechten Bretter auseinanderdrücken.
+Das erzeugt genau diese gefährliche Zugspannung quer zur Faser.
+Noch dazu gibt es Spannungskonzentrationen an den Ecken der Aussparungen.
+Da können Längsrisse entstehen, die sich dann ausbreiten.
+Viel sicherer ist es, wenn die Keile oben und unten angreifen.
+Dort arbeiten sie mehr in Richtung Querdruckspannung.
+Das lässt sich kontrollieren und führt nicht zu Aufspaltung.
+Außerdem sollte die Keilneigung wirklich flach sein, höchstens eins zu zehn.
+Sonst wird die Kraft zu konzentriert und man beschädigt die Holzfasern.
+Am Ende geht es darum: kein Messer, das die Fasern auftrennt, sondern ein Spanner, der eine Verzahnung fest hält.</t>
+  </si>
+  <si>
+    <t>En construcciones de madera siempre hay que pensar en los mecanismos típicos de fallo.
+La madera soporta la compresión paralela a la fibra excelentemente.
+También la compresión perpendicular funciona medianamente, ahí hay aplastamiento pero no rotura.
+Lo crítico es la tracción perpendicular a la fibra.
+Ese es el caso clásico: "la madera se ha abierto", o sea, partido.
+Por eso nunca usaría cuñas que empujen las tablas verticales separándolas.
+Eso genera exactamente esa peligrosa tracción perpendicular a la fibra.
+Encima hay concentraciones de tensión en las esquinas de los cajeados.
+Ahí pueden aparecer fisuras longitudinales que luego se propagan.
+Mucho más seguro es que las cuñas actúen arriba y abajo.
+Allí trabajan más en dirección de compresión transversal.
+Eso se puede controlar y no lleva a rajaduras.
+Además la inclinación de la cuña debería ser realmente suave, como mucho uno a diez.
+Si no, la fuerza se concentra demasiado y se dañan las fibras de la madera.
+Al final se trata de: no un cuchillo que separa las fibras, sino un tensor que sujeta firme un encaje.</t>
+  </si>
+  <si>
+    <t>Holzbau_4</t>
+  </si>
+  <si>
+    <t>Holzbau_5</t>
+  </si>
+  <si>
+    <t>Holzbau_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El problema de la dirección </t>
+  </si>
+  <si>
+    <t>Pass mal auf, hier liegt der Knackpunkt.
+Wir müssen genau überlegen, wie wir die Keile einsetzen.
+Wenn wir die Keile vertikal einsetzen, also von oben nach unten,
+dann üben wir Druck auf die horizontalen Bretter aus.
+Das ist noch okay, Holz verträgt Druck ganz gut.
+Aber wenn wir die Keile so einsetzen, dass sie die vertikalen Bretter aufspreizen,
+dann wird es gefährlich.
+Denn dann erzeugen wir Zug senkrecht zur Faser.
+Und das ist quasi der Tod für Holz.
+Das Holz reißt dann ganz schnell, es entstehen Risse.
+Das wollen wir auf keinen Fall.
+Deshalb ist meine klare Empfehlung:
+Wir arbeiten lieber mit horizontalen Keilen.
+Die drücken die Module seitlich zusammen.
+Das ist viel sicherer für das Material.
+Wir wollen ja die Verbindung festziehen, nicht das Holz zerstören.
+Verstehst du, worauf ich hinauswill?
+Es geht um die Richtung der Kraft im Verhältnis zur Faser.</t>
+  </si>
+  <si>
+    <t>Oye mira, aquí está el punto clave.
+Tenemos que pensar exactamente cómo insertamos las cuñas.
+Si insertamos las cuñas verticalmente, es decir, de arriba a abajo,
+entonces ejercemos presión sobre los tableros horizontales.
+Eso todavía está bien, la madera aguanta bastante bien la presión.
+Pero si insertamos las cuñas de tal manera que abran los tableros verticales,
+entonces se vuelve peligroso.
+Porque entonces generamos tracción perpendicular a la fibra.
+Y eso es prácticamente la muerte para la madera.
+La madera se raja entonces muy rápido, se producen grietas.
+Eso no lo queremos bajo ningún concepto.
+Por eso es mi recomendación clara:
+Trabajamos mejor con cuñas horizontales.
+Esas aprietan los módulos lateralmente.
+Eso es mucho más seguro para el material.
+Queremos apretar la unión, no destruir la madera.
+¿Entiendes a qué quiero llegar?
+Se trata de la dirección de la fuerza en relación con la fibra.</t>
+  </si>
+  <si>
+    <t> Cortante y Bloqueo</t>
+  </si>
+  <si>
+    <t>Stell dir vor, der Wind drückt gegen die Wand.
+Was passiert dann physikalisch?
+Die einzelnen Module wollen sich gegeneinander verschieben.
+Das nennen wir Schubkraft oder Scherung.
+Es ist wie bei einem Kartenspiel, wenn man oben dagegen stößt.
+Die Karten verrutschen.
+Genau das müssen wir verhindern.
+Jetzt kommt die Frage: Wie stoppen wir das?
+Nur mit Reibung? Nein, das ist zu unsicher.
+Wenn wir nur von oben draufdrücken, entsteht zwar Reibung,
+aber es kann trotzdem noch mikroskopisch verrutschen.
+Das ist zu weich.
+Wir brauchen einen richtigen Formschluss.
+Das heißt, wir brauchen etwas, das physikalisch im Weg ist.
+Wie ein Riegel oder ein Stift.
+Unsere horizontalen Keile übernehmen genau diese Aufgabe.
+Sie füllen den Spalt zwischen den Modulen aus.
+Sie blockieren die Bewegung direkt in die Richtung, wo der Wind hinwill.
+Also nicht nur von oben pressen, sondern seitlich verkeilen.
+Dann arbeitet das Ganze wie ein einziger großer Block.
+Das macht die Wand steif und stabil.</t>
+  </si>
+  <si>
+    <t>Imagínate que el viento empuja contra la pared.
+¿Qué pasa entonces físicamente?
+Los módulos individuales quieren desplazarse unos contra otros.
+A eso lo llamamos fuerza de cortante o cizallamiento.
+Es como con una baraja de cartas, cuando empujas desde arriba.
+Las cartas se deslizan.
+Exactamente eso tenemos que evitarlo.
+Ahora viene la pregunta: ¿Cómo paramos eso?
+¿Solo con fricción? No, eso es demasiado inseguro.
+Si solo apretamos desde arriba, aunque surge fricción,
+puede seguir deslizándose microscópicamente.
+Eso es demasiado blando.
+Necesitamos un verdadero cierre de forma (bloqueo geométrico).
+Eso significa que necesitamos algo que esté físicamente en el camino.
+Como un cerrojo o un pasador.
+Nuestras cuñas horizontales asumen exactamente esta tarea.
+Rellenan el hueco entre los módulos.
+Bloquean el movimiento directamente en la dirección hacia donde quiere ir el viento.
+Así que no solo apretar desde arriba, sino enclavar lateralmente.
+Entonces el conjunto trabaja como un único bloque grande.
+Eso vuelve la pared rígida y estable.</t>
+  </si>
+  <si>
+    <t>Detalles de Construcción </t>
+  </si>
+  <si>
+    <t>Lass uns über die praktische Umsetzung sprechen.
+Welches Holz nehmen wir für die Keile?
+Ich würde auf jeden Fall Buche nehmen.
+Buche ist hart und druckfest.
+Das ist wichtig, weil die Keile ja richtig arbeiten müssen.
+Und noch ein wichtiger Punkt: die Neigung der Keile.
+Mach sie nicht zu steil!
+Eine Neigung von 1 zu 10 oder 1 zu 15 ist ideal.
+Wenn der Winkel zu steil ist, wirkt die Keile zu aggressiv.
+Sie könnte das Holz wieder aufsprengen.
+Wir wollen eine sanfte Vorspannung.
+Außerdem müssen wir an die Zukunft denken.
+Holz arbeitet, es schwindet und quillt.
+Nach ein paar Monaten wird sich das System ein bisschen setzen.
+Deshalb ist es genial, wenn die Keile zugänglich bleiben.
+Man muss sie später nachschlagen oder nachjustieren können.
+Das ist der Vorteil von dieser trockenen Bauweise.
+Es ist nicht starr wie Beton, es ist lebendig.
+Solange wir das Spielraum entfernen und den Kontakt erzwingen,
+funktioniert das System als semirigide Wand.
+Und das reicht für unsere Zwecke völlig aus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hablemos de la implementación práctica.
+¿Qué madera tomamos para las cuñas?
+Yo cogería sin duda haya.
+El haya es duro y resistente a la presión.
+Eso es importante, porque las cuñas tienen que trabajar de verdad.
+Y otro punto importante: la inclinación de las cuñas.
+¡No las hagas demasiado empinadas!
+Una pendiente de 1 a 10 o 1 a 15 es ideal.
+Si el ángulo es demasiado empinado, la cuña actúa demasiado agresiva.
+Podría volver a reventar la madera.
+Queremos una pretensión suave.
+Además tenemos que pensar en el futuro.
+La madera trabaja, se contrae y se hincha.
+Después de unos meses el sistema se asentará un poco.
+Por eso es genial si las cuñas permanecen accesibles.
+Hay que poder golpearlas o reajustarlas más tarde.
+Esa es la ventaja de este tipo de construcción en seco.
+No es rígido como el hormigón, es vivo.
+Mientras eliminemos la holgura y forcemos el contacto,
+el sistema funciona como una pared semirrígida.
+Y eso es totalmente suficiente para nuestros propósitos.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,6 +805,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFF4F0EB"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -551,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -570,6 +851,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1320,101 +1602,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="4"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="4"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="4"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="4"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
+    <row r="24" spans="1:6" ht="208" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="208" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="208.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="273.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
-      <c r="B30" s="1"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="3"/>
       <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
-      <c r="B32" s="1"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
-      <c r="B35" s="1"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
-      <c r="B36" s="1"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C593BE-6808-4E3E-ADD8-7247E7CF8FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6584BAD-2F7E-4DDD-9BD7-76B9DF0423C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
   <si>
     <t>Isla</t>
   </si>
@@ -770,6 +770,61 @@
 el sistema funciona como una pared semirrígida.
 Y eso es totalmente suficiente para nuestros propósitos.
 </t>
+  </si>
+  <si>
+    <t>So, ich fange jetzt mit dem Kochen an.
+Kannst du mir die große Schüssel da oben rausholen?
+Die steht ganz hinten im Schrank drin.
+Ah, perfekt, danke! Stell sie einfach hier hin, wenn du willst.</t>
+  </si>
+  <si>
+    <t>Bueno, me voy a poner a cocinar ahora mismo.
+¿Puedes sacar el bol grande del armario de ahí arriba?
+Está justo al fondo.
+Ah, perfecto, ¡gracias! Déjalo aquí si quieres.</t>
+  </si>
+  <si>
+    <t>Weißt du was, hol doch auch gleich die Gewürze runter, die brauch ich sowieso.
+Genau, die da. Keine Sorge, ich stell sie nachher wieder rein.
+Ach, und nimm bitte auch die Milch aus dem Kühlschrank raus.
+Die kannst du direkt hier hinstellen, dann hab ich alles griffbereit.</t>
+  </si>
+  <si>
+    <t>Oye, ya que estás, baja también las especias, que las voy a necesitar de todas formas.
+Esas, sí. Luego no te preocupes que las vuelvo a dejar en su sitio.
+Ah, y saca también la leche de la nevera, por favor.
+Puedes ponerla directamente aquí, así tengo todo a mano.</t>
+  </si>
+  <si>
+    <t>Espera un momento... esa caja con las verduras estorba ahí un montón.
+¿Puedes apartarla un poco? Casi mejor que saques las verduras y las coloques en la nevera en los cajones de abajo. Mira a ver si se ha puesto algo malo y lo tiras ya que estás. Es que tenemos la nevera a reventar.
+Buenos pues genial, así tengo mucho más espacio.</t>
+  </si>
+  <si>
+    <t>Moment mal... die Kiste mit dem Gemüse stört da total.
+Kannst du die mal ein bisschen zur Seite schieben?
+Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Unser Kühlschrank ist nämlich total vollgestopft!
+Super, so hab ich viel mehr Platz.</t>
+  </si>
+  <si>
+    <t>Ich geh ganz kurz rüber zum Nachbarn, der wollte mir noch Eier vorbeibringen.
+Bin in zwei Minuten wieder da, ja?
+So, da bin ich wieder. Wo soll ich die Eier hinlegen? Hast du den letzten Karton weggeworfen? Ah, ich seh ihn schon, der stand genau hinter der Tupperdose mit den Makkaroni.</t>
+  </si>
+  <si>
+    <t>Voy un segundo a casa del vecino, que me iba a traer huevos.
+Vuelvo en dos minutos, ¿vale?
+Ya está, ya estoy aquí. ¿Dónde guardo los huevos? ¿Tiraste el último cartón? Ah, ya lo veo, estaba justo detrás del táper de macarrones.</t>
+  </si>
+  <si>
+    <t>¿Me pasas la sal un momento? ¡Gracias!
+Bueno, ahora saco la carne y la frío directamente en la sartén.
+Mmm, huele bien ya, ¿no te parece? ¡Hoy vamos a comer de lo lindo!</t>
+  </si>
+  <si>
+    <t>Reichst du mir mal eben das Salz rüber? Danke dir!
+So, jetzt nehm ich das Fleisch raus und brate es direkt in der Pfanne an.
+Mmm, riecht schon gut, findest du nicht? Heute lassen wir es uns richtig gut schmecken!</t>
   </si>
 </sst>
 </file>
@@ -854,7 +909,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1132,17 +1187,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="80.90625" customWidth="1"/>
-    <col min="3" max="3" width="78.453125" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" customWidth="1"/>
-    <col min="6" max="6" width="7.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.4609375" customWidth="1"/>
+    <col min="2" max="2" width="80.921875" customWidth="1"/>
+    <col min="3" max="3" width="78.4609375" customWidth="1"/>
+    <col min="4" max="4" width="10.07421875" customWidth="1"/>
+    <col min="5" max="5" width="33.84375" customWidth="1"/>
+    <col min="6" max="6" width="7.23046875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1162,7 +1218,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="51.45" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1182,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1202,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="39" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1262,7 +1318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -1282,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -1302,7 +1358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -1322,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -1342,7 +1398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
@@ -1362,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -1382,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -1402,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -1422,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1442,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -1462,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1482,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="129" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
@@ -1502,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="143.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="141.9" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
@@ -1522,7 +1578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="156.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="154.75" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1542,15 +1598,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="273.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>91</v>
@@ -1562,267 +1618,367 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="286.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="58.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="234.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="219" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="208" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="208" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="208.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="234.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="273.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="206.15" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="231.9" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="4"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="4"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="4"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="4"/>
       <c r="B35" s="8"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="4"/>
       <c r="B36" s="8"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
       <c r="B37" s="8"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="4"/>
       <c r="B38" s="8"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="4"/>
       <c r="B39" s="8"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="4"/>
-      <c r="B40" s="1"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="4"/>
-      <c r="B41" s="1"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
-      <c r="B42" s="1"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="4"/>
-      <c r="B43" s="1"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="4"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="4"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A47" s="4"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A48" s="4"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A49" s="4"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A50" s="4"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A51" s="4"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6584BAD-2F7E-4DDD-9BD7-76B9DF0423C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3E0F4F-CFFE-4FAA-94BD-53F9A230283A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="135">
   <si>
     <t>Isla</t>
   </si>
@@ -363,45 +363,6 @@
   </si>
   <si>
     <t>Movimiento (Cocina / Convivencia)</t>
-  </si>
-  <si>
-    <t>So, ich fange jetzt mit dem Kochen an.
-Kannst du mir die große Schüssel da oben rausholen?
-Die steht ganz hinten im Schrank drin.
-Ah, perfekt, danke! Stell sie einfach hier hin, wenn du willst.
-Weißt du was, hol doch auch gleich die Gewürze runter, die brauch ich sowieso.
-Genau, die da. Keine Sorge, ich stell sie nachher wieder rein.
-Ach, und nimm bitte auch die Milch aus dem Kühlschrank raus.
-Die kannst du direkt hier hinstellen, dann hab ich alles griffbereit.
-Moment mal... die Kiste mit dem Gemüse stört da total.
-Kannst du die mal ein bisschen zur Seite schieben?
-Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Schau mal, ob etwas schlecht geworden ist, und wirf es direkt weg, wenn du schon dabei bist. Unser Kühlschrank ist nämlich total vollgestopft!
-Super, so hab ich viel mehr Platz.
-Ich geh ganz kurz rüber zum Nachbarn, der wollte mir noch Eier vorbeibringen.
-Bin in zwei Minuten wieder da, ja?
-So, da bin ich wieder. Wo soll ich die Eier hinlegen? Hast du den letzten Karton weggeworfen? Ah, ich seh ihn schon, der stand genau hinter der Tupperdose mit den Makkaroni.
-Reichst du mir mal eben das Salz rüber? Danke dir!
-So, jetzt nehm ich das Fleisch raus und brate es direkt in der Pfanne an.
-Mmm, riecht schon gut, findest du nicht? Heute lassen wir es uns richtig gut schmecken!</t>
-  </si>
-  <si>
-    <t>Bueno, me voy a poner a cocinar ahora mismo.
-¿Puedes sacar el bol grande del armario de ahí arriba?
-Está justo al fondo.
-Ah, perfecto, ¡gracias! Déjalo aquí si quieres.
-Oye, ya que estás, baja también las especias, que las voy a necesitar de todas formas.
-Esas, sí. Luego no te preocupes que las vuelvo a dejar en su sitio.
-Ah, y saca también la leche de la nevera, por favor.
-Puedes ponerla directamente aquí, así tengo todo a mano.
-Espera un momento... esa caja con las verduras estorba ahí un montón.
-¿Puedes apartarla un poco? Casi mejor que saques las verduras y las coloques en la nevera en los cajones de abajo. Mira a ver si se ha puesto algo malo y lo tiras ya que estás. Es que tenemos la nevera a reventar.
-Buenos pues genial, así tengo mucho más espacio.
-Voy un segundo a casa del vecino, que me iba a traer huevos.
-Vuelvo en dos minutos, ¿vale?
-Ya está, ya estoy aquí. ¿Dónde guardo los huevos? ¿Tiraste el último cartón? Ah, ya lo veo, estaba justo detrás del táper de macarrones.
-¿Me pasas la sal un momento? ¡Gracias!
-Bueno, ahora saco la carne y la frío directamente en la sartén.
-Mmm, huele bien ya, ¿no te parece? ¡Hoy vamos a comer de lo lindo!</t>
   </si>
   <si>
     <t>Bueno, hoy por fin voy a ordenar el salón.
@@ -784,12 +745,6 @@
 Ah, perfecto, ¡gracias! Déjalo aquí si quieres.</t>
   </si>
   <si>
-    <t>Weißt du was, hol doch auch gleich die Gewürze runter, die brauch ich sowieso.
-Genau, die da. Keine Sorge, ich stell sie nachher wieder rein.
-Ach, und nimm bitte auch die Milch aus dem Kühlschrank raus.
-Die kannst du direkt hier hinstellen, dann hab ich alles griffbereit.</t>
-  </si>
-  <si>
     <t>Oye, ya que estás, baja también las especias, que las voy a necesitar de todas formas.
 Esas, sí. Luego no te preocupes que las vuelvo a dejar en su sitio.
 Ah, y saca también la leche de la nevera, por favor.
@@ -801,12 +756,6 @@
 Buenos pues genial, así tengo mucho más espacio.</t>
   </si>
   <si>
-    <t>Moment mal... die Kiste mit dem Gemüse stört da total.
-Kannst du die mal ein bisschen zur Seite schieben?
-Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Unser Kühlschrank ist nämlich total vollgestopft!
-Super, so hab ich viel mehr Platz.</t>
-  </si>
-  <si>
     <t>Ich geh ganz kurz rüber zum Nachbarn, der wollte mir noch Eier vorbeibringen.
 Bin in zwei Minuten wieder da, ja?
 So, da bin ich wieder. Wo soll ich die Eier hinlegen? Hast du den letzten Karton weggeworfen? Ah, ich seh ihn schon, der stand genau hinter der Tupperdose mit den Makkaroni.</t>
@@ -825,6 +774,30 @@
     <t>Reichst du mir mal eben das Salz rüber? Danke dir!
 So, jetzt nehm ich das Fleisch raus und brate es direkt in der Pfanne an.
 Mmm, riecht schon gut, findest du nicht? Heute lassen wir es uns richtig gut schmecken!</t>
+  </si>
+  <si>
+    <t>Bewegung_4</t>
+  </si>
+  <si>
+    <t>Bewegung_5</t>
+  </si>
+  <si>
+    <t>Bewegung_20</t>
+  </si>
+  <si>
+    <t>Bewegung_30</t>
+  </si>
+  <si>
+    <t>Weißt du was, hol doch auch gleich die Gewürze runter, die brauch ich sowieso.
+Genau, die da. Keine Sorge, ich stell sie nachher wieder rein.
+Ach, und nimm bitte auch die Milch aus dem Kühlschrank raus.
+Die kannst du direkt hier hinstellen, dann habe ich alles griffbereit.</t>
+  </si>
+  <si>
+    <t>Moment mal... die Kiste mit dem Gemüse stört da total.
+Kannst du die mal ein bisschen zur Seite schieben?
+Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Schau mal, ob etwas schlecht geworden ist, und wirf es direkt weg, wenn du schon dabei bist. Unser Kühlschrank ist nämlich total vollgestopft!
+Super, so hab ich viel mehr Platz.</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.4609375" customWidth="1"/>
@@ -1603,13 +1576,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>86</v>
@@ -1623,13 +1596,13 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>86</v>
@@ -1643,10 +1616,10 @@
         <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>91</v>
@@ -1663,13 +1636,13 @@
         <v>85</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>86</v>
@@ -1683,13 +1656,13 @@
         <v>85</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>86</v>
@@ -1703,56 +1676,56 @@
         <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" ht="219" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="219" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>95</v>
+      <c r="E28" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
@@ -1760,123 +1733,109 @@
     </row>
     <row r="29" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="206.15" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F30" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="206.15" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" ht="231.9" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="231.9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F33" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0</v>
-      </c>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="4"/>
@@ -1934,7 +1893,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="4"/>
-      <c r="B44" s="8"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
@@ -1973,12 +1932,6 @@
       <c r="B50" s="1"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A51" s="4"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3E0F4F-CFFE-4FAA-94BD-53F9A230283A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B934B3D-C91A-4EE2-BE40-26D24C0EBB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
   <si>
     <t>Isla</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Wann fängt der Kurs an? Das ist eine gute Frage. Soweit ich weiß, geht es erst im Oktober los. Alles in allem haben wir also noch genug Zeit für die Anmeldung.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Cuándo empieza el curso? Esa es una buena pregunta. Que yo sepa, no empieza hasta octubre. En resumen, todavía tenemos tiempo de sobra para apuntarnos. </t>
   </si>
   <si>
     <t xml:space="preserve">Sollen wir dieses Jahr nach Asien reisen? Das ist ein guter Punkt, aber ich habe mir noch keine Gedanken darüber gemacht. Lass mich kurz nachdenken... Vielleicht ist es zu teuer.  </t>
@@ -354,9 +351,6 @@
   </si>
   <si>
     <t>FH_3</t>
-  </si>
-  <si>
-    <t>Dominio</t>
   </si>
   <si>
     <t>Bewegung</t>
@@ -798,6 +792,19 @@
 Kannst du die mal ein bisschen zur Seite schieben?
 Am besten nimmst du das Gemüse raus und legst es unten in die Schubladen vom Kühlschrank rein. Schau mal, ob etwas schlecht geworden ist, und wirf es direkt weg, wenn du schon dabei bist. Unser Kühlschrank ist nämlich total vollgestopft!
 Super, so hab ich viel mehr Platz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuándo empieza el curso? Esa es una buena pregunta. Que yo sepa, no empieza hasta octubre. En resumidas cuentas (al fin y al cabo), todavía tenemos tiempo de sobra para apuntarnos. </t>
+  </si>
+  <si>
+    <t>Explicacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se podria decir tambien: Eigentlich schon, aber das Wetter soll schlecht werden. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wann fängt der Kurs an? 
+Wann fangen wir den Kurs an? </t>
   </si>
 </sst>
 </file>
@@ -860,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -873,13 +880,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,7 +1172,7 @@
     <col min="3" max="3" width="78.4609375" customWidth="1"/>
     <col min="4" max="4" width="10.07421875" customWidth="1"/>
     <col min="5" max="5" width="33.84375" customWidth="1"/>
-    <col min="6" max="6" width="7.23046875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="103.84375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -1185,10 +1189,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>84</v>
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.45" x14ac:dyDescent="0.4">
@@ -1202,13 +1206,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1222,13 +1226,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1242,13 +1243,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1262,33 +1260,30 @@
         <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1296,19 +1291,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1316,19 +1308,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1336,19 +1325,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1356,19 +1342,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1376,19 +1359,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
@@ -1396,526 +1376,460 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="26.15" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="129" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:5" ht="129" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="141.9" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="141.9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="154.75" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="154.75" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="4" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="51.9" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="283.3" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="58.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="D26" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="219" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" s="1" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="205.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="219" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="E28" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="205.75" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="206.15" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="205.75" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="E30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="206.15" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:5" ht="231.9" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="270.45" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="231.9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="E32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="4" t="s">
+    </row>
+    <row r="33" spans="1:5" ht="283.3" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="270.45" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="283.3" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="4"/>
-      <c r="B34" s="8"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" s="4"/>
-      <c r="B35" s="8"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="3"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" s="4"/>
-      <c r="B36" s="8"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
-      <c r="B37" s="8"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" s="4"/>
-      <c r="B38" s="8"/>
+      <c r="B38" s="6"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" s="4"/>
-      <c r="B39" s="8"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" s="4"/>
-      <c r="B40" s="8"/>
+      <c r="B40" s="6"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" s="4"/>
-      <c r="B41" s="8"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
-      <c r="B42" s="8"/>
+      <c r="B42" s="6"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" s="4"/>
-      <c r="B43" s="8"/>
+      <c r="B43" s="6"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" s="4"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" s="4"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" s="4"/>
       <c r="B47" s="1"/>
       <c r="C47" s="3"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" s="4"/>
       <c r="B48" s="1"/>
       <c r="C48" s="3"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B934B3D-C91A-4EE2-BE40-26D24C0EBB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAA58B6-C5AA-4AE8-BD4A-6307CC6152C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="139">
   <si>
     <t>Isla</t>
   </si>
@@ -804,14 +804,92 @@
   </si>
   <si>
     <t xml:space="preserve">Wann fängt der Kurs an? 
-Wann fangen wir den Kurs an? </t>
+Wann fangen wir den Kurs an? 
+"Erst" + fecha 
+Anfangen es más técnico/escolar ("El curso empieza a las 9").
+Losgehen es más dinámico ("¿Cuándo arranca esto?", "¡Ya empezó el lío!").
+Das startet erst im Oktober.
+Der Kurs beginnt erst im Oktober. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Das kann ich mir kaum vorstellen"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apenas puedo imaginarme eso.
+Eso no me lo creo.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Auf keinen Fall mache ich das mit!" 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>De ninguna manera me apunto a eso!"
+ "¡Ni hablar, yo no entro en ese juego!"
+ "no cuentes conmigo para eso"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Ich mache mit / Ich bin dabei!: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Me apunto, cuenten conmigo. </t>
+    </r>
+  </si>
+  <si>
+    <t>"Dabei geht es um..." 
+"Es geht um..."
+"Das Thema ist…" 
+"Hier dreht sich alles um das…" 
+[Verbo movimiento]+um eine Stunde = en una hora
+"Wir verschieben das Treffen um eine Stunde." Moveremos la reunión una hora: si era a las 10:00, ahora es a las 11:00.  
+"Wir verschieben das Treffen auf eine Stunde." Posponemos la reunión a la una en punto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,6 +924,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -867,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -882,6 +968,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1266,7 +1355,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="102" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1392,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -1318,6 +1407,9 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>65</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1371,7 +1463,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="51.9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="102" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -1386,6 +1478,9 @@
       </c>
       <c r="E12" s="1" t="s">
         <v>69</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
@@ -1609,7 +1704,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="283.3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" ht="270.45" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
         <v>83</v>
       </c>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAA58B6-C5AA-4AE8-BD4A-6307CC6152C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5E4D8B-8148-4951-97D0-79A370B55179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,13 +876,13 @@
     </r>
   </si>
   <si>
-    <t>"Dabei geht es um..." 
-"Es geht um..."
-"Das Thema ist…" 
-"Hier dreht sich alles um das…" 
-[Verbo movimiento]+um eine Stunde = en una hora
-"Wir verschieben das Treffen um eine Stunde." Moveremos la reunión una hora: si era a las 10:00, ahora es a las 11:00.  
-"Wir verschieben das Treffen auf eine Stunde." Posponemos la reunión a la una en punto</t>
+    <t>"Dabei geht es um...".
+"Es geht um...".
+"Das Thema ist…" .
+"Hier dreht sich alles um das…" .
+[Verbo movimiento]+um eine Stunde = en una hora.
+"Wir verschieben das Treffen um eine Stunde" Moveremos la reunión una hora, si era a las 10:00, ahora es a las 11:00.  
+"Wir verschieben das Treffen auf eine Stunde" Posponemos la reunión a la una en punto.</t>
   </si>
 </sst>
 </file>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5E4D8B-8148-4951-97D0-79A370B55179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A95D0AD-7694-4089-8131-7BC2B5426D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,13 +876,57 @@
     </r>
   </si>
   <si>
-    <t>"Dabei geht es um...".
-"Es geht um...".
-"Das Thema ist…" .
-"Hier dreht sich alles um das…" .
-[Verbo movimiento]+um eine Stunde = en una hora.
-"Wir verschieben das Treffen um eine Stunde" Moveremos la reunión una hora, si era a las 10:00, ahora es a las 11:00.  
-"Wir verschieben das Treffen auf eine Stunde" Posponemos la reunión a la una en punto.</t>
+    <r>
+      <t xml:space="preserve">"&lt;b&gt;Dabei geht es um...&lt;b&gt;".
+"&lt;b&gt;Es geht um...&lt;b&gt;".
+"&lt;b&gt;Das Thema ist…&lt;b&gt;" .
+"&lt;b&gt;Hier dreht sich alles um das…&lt;b&gt;" .
+[Verbo movimiento]+&lt;b&gt;um&lt;b&gt; eine Stunde = en una hora.
+"Wir verschieben das Treffen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>um</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> eine Stunde" Moveremos la reunión una hora, si era a las 10:00, ahora es a las 11:00.  
+"Wir verschieben das Treffen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>auf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> eine Stunde" Posponemos la reunión a la una en punto.</t>
+    </r>
   </si>
 </sst>
 </file>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A95D0AD-7694-4089-8131-7BC2B5426D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49362F0B-EE57-482B-BDFA-AF467B2080D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -877,12 +877,12 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">"&lt;b&gt;Dabei geht es um...&lt;b&gt;".
-"&lt;b&gt;Es geht um...&lt;b&gt;".
-"&lt;b&gt;Das Thema ist…&lt;b&gt;" .
-"&lt;b&gt;Hier dreht sich alles um das…&lt;b&gt;" .
-[Verbo movimiento]+&lt;b&gt;um&lt;b&gt; eine Stunde = en una hora.
-"Wir verschieben das Treffen </t>
+      <t xml:space="preserve">"Dabei geht es um...".
+"Es geht um...".
+"Das Thema ist…" .
+"Hier dreht sich alles um das…" .
+[Verbo movimiento]+um eine Stunde = en una hora.
+Wir verschieben das Treffen </t>
     </r>
     <r>
       <rPr>
@@ -903,8 +903,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> eine Stunde" Moveremos la reunión una hora, si era a las 10:00, ahora es a las 11:00.  
-"Wir verschieben das Treffen </t>
+      <t xml:space="preserve"> eine Stunde. 
+Moveremos la reunión una hora, si era a las 10:00, ahora es a las 11:00.  
+Wir verschieben das Treffen </t>
     </r>
     <r>
       <rPr>
@@ -925,7 +926,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> eine Stunde" Posponemos la reunión a la una en punto.</t>
+      <t xml:space="preserve"> eine Stunde.
+Posponemos la reunión a la una en punto.</t>
     </r>
   </si>
 </sst>
@@ -1507,7 +1509,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="102" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="131.15" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alber\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49362F0B-EE57-482B-BDFA-AF467B2080D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4EE1D-B90A-4A81-A043-233CE3003036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
   <si>
     <t>Isla</t>
   </si>
@@ -929,6 +929,34 @@
       <t xml:space="preserve"> eine Stunde.
 Posponemos la reunión a la una en punto.</t>
     </r>
+  </si>
+  <si>
+    <t>Chunks_12</t>
+  </si>
+  <si>
+    <t>Chunks_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir können uns diesen Urlaub dieses Jahr einfach nicht leisten! Ich bin der festen Überzeugung, dass wir im Moment jeden Cent sparen müssen. Das ist ein gutes Argument, aber wir arbeiten beide so viel und brauchen einfach mal eine Pause. 
+Na ja, es steht fest, dass wir uns bald entscheiden müssen.  </t>
+  </si>
+  <si>
+    <t>¡Este año simplemente no podemos permitirnos esas vacaciones! Estoy firmemente convencido de que en este momento tenemos que ahorrar cada céntimo. Ese es un buen argumento, pero los dos trabajamos un montón y necesitamos un descanso sí o sí. En fin, está claro que tenemos que decidirnos pronto.</t>
+  </si>
+  <si>
+    <t>Dar una opinión firme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicar cómo hacer algo paso a paso    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie backt man diesen Kuchen?
+Das ist gar nicht so schwer. 
+Pass auf: Du brauchst nur Mehl, Zucker und Eier. 
+Mach dir keine Sorgen, das kriegst du schon hin! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cómo se hace esta tarta? No es tan difícil. Escucha: solo necesitas harina, azúcar y huevos. No te preocupes, ¡ya verás como te sale! </t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1049,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1299,18 +1327,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.4609375" customWidth="1"/>
-    <col min="2" max="2" width="80.921875" customWidth="1"/>
-    <col min="3" max="3" width="78.4609375" customWidth="1"/>
-    <col min="4" max="4" width="10.07421875" customWidth="1"/>
-    <col min="5" max="5" width="33.84375" customWidth="1"/>
-    <col min="6" max="6" width="103.84375" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="80.90625" customWidth="1"/>
+    <col min="3" max="3" width="78.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="5" width="33.81640625" customWidth="1"/>
+    <col min="6" max="6" width="103.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1358,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="51.45" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="52" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1350,7 +1378,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1367,7 +1395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1384,7 +1412,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="39" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1401,7 +1429,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="102" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1421,7 +1449,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -1438,7 +1466,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -1458,7 +1486,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -1475,7 +1503,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -1492,7 +1520,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
@@ -1509,7 +1537,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -1529,464 +1557,500 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>144</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="26.15" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26.15" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="129" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="141.9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="154.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="143.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="51.9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="270.45" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="219" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="205.75" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="205.75" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="206.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" ht="208" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="231.9" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="208" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="270.45" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="208.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>115</v>
+      <c r="B32" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="283.3" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="273.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="6"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="6"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="6"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="6"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="6"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="6"/>
       <c r="C41" s="3"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="6"/>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="6"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="6"/>
       <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
-      <c r="B45" s="1"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="3"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="1"/>
       <c r="C47" s="3"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="1"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="1"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="1"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="4"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="4"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4EE1D-B90A-4A81-A043-233CE3003036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A710BBD6-5517-4EC2-8CEF-E30616FE2AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="155">
   <si>
     <t>Isla</t>
   </si>
@@ -957,6 +957,34 @@
   </si>
   <si>
     <t xml:space="preserve">¿Cómo se hace esta tarta? No es tan difícil. Escucha: solo necesitas harina, azúcar y huevos. No te preocupes, ¡ya verás como te sale! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallo! Wo ist mein Buch? 
+Es ist mir ein bisschen peinlich, aber ich habe es zu Hause gelassen. 
+Ich habe es total vergessen.
+ — Das macht nichts, du kannst es mir morgen geben.  </t>
+  </si>
+  <si>
+    <t>Chunks_14</t>
+  </si>
+  <si>
+    <t>Chunks_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¡Hola! ¿Dónde está mi libro? Me da un poco de vergüenza, pero lo he dejado en casa. Se me olvidó por completo. — No pasa nada, me lo puedes dar mañana. </t>
+  </si>
+  <si>
+    <t>Salvar una situación incómoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expresar decepción o alivio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schade, dass das Konzert gestern wegen Regen abgesagt wurde. 
+Aber Gott sei Dank! haben wir das Geld für die Tickets zurückbekommen. Glück gehabt!  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qué pena que se cancelara el concierto de ayer por la lluvia. Pero ¡menos mal! que nos han devuelto el dinero de las entradas. ¡Qué suerte hemos tenido! </t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
@@ -1593,55 +1621,57 @@
       </c>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
@@ -1649,149 +1679,149 @@
         <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="143.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="143.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>84</v>
@@ -1802,165 +1832,187 @@
         <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="208" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="208" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="208.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="208" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="208" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="273.5" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="208.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>115</v>
+      <c r="B34" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="273.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="4"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
@@ -2012,13 +2064,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
-      <c r="B46" s="1"/>
+      <c r="B46" s="6"/>
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
-      <c r="B47" s="1"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="3"/>
       <c r="D47" s="4"/>
     </row>
@@ -2051,6 +2103,18 @@
       <c r="B52" s="1"/>
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="4"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="4"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alberto.calvo.STEKO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A710BBD6-5517-4EC2-8CEF-E30616FE2AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDB1529-958F-43E1-8DE7-FC667BD3975F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="176">
   <si>
     <t>Isla</t>
   </si>
@@ -985,6 +985,94 @@
   </si>
   <si>
     <t xml:space="preserve">Qué pena que se cancelara el concierto de ayer por la lluvia. Pero ¡menos mal! que nos han devuelto el dinero de las entradas. ¡Qué suerte hemos tenido! </t>
+  </si>
+  <si>
+    <t>Chunks_16</t>
+  </si>
+  <si>
+    <t>Chunks_17</t>
+  </si>
+  <si>
+    <t>Chunks_18</t>
+  </si>
+  <si>
+    <t>Chunks_19</t>
+  </si>
+  <si>
+    <t>Defender tu punto de vista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aus meiner Sicht ist die neue Strategie nicht optimal. 
+Im Vergleich zu unserem alten System ist sie viel zu kompliziert. 
+Das hat keinen Wert, wenn wir dadurch Zeit verlieren.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde mi punto de vista, la nueva estrategia no es óptima. En comparación con nuestro sistema antiguo, es demasiado complicada. Eso no sirve para nada si perdemos tiempo con ello. </t>
+  </si>
+  <si>
+    <t>Interrumpir educadamente en una reunión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darf ich kurz unterbrechen? 
+Ich wollte nur sagen, dass wir das Budget nicht vergessen dürfen. Ansonsten hast du da absolut recht, die Idee ist super. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Puedo interrumpir un momento? Solo quería decir que no nos podemos olvidar del presupuesto. 
+Por lo demás, en eso tienes toda la razón, la idea es buenísima. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hablar de salud o estado físico </t>
+  </si>
+  <si>
+    <t>In der letzten Zeit trinke ich keinen Kaffee mehr.
+Am Anfang war es schwer, aber Fast Food kommt für mich auch nicht mehr infrage.
+Ich muss mich daran gewöhnen, mehr Tee zu trinken.
+Manchmal vermisse ich den Geschmack, aber meine Gesundheit geht einfach vor.</t>
+  </si>
+  <si>
+    <t>Últimamente ya no tomo café.
+Al principio fue difícil, pero la comida rápida tampoco es una opción para mí ya.
+Tengo que acostumbrarme a tomar más té.
+A veces echo de menos el sabor, pero mi salud es lo primero, simplemente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedir explicaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich verstehe den Plan nicht ganz. 
+Könnten Sie das genauer erklären? 
+Auf den ersten Blick klingt es gut, aber wie bereits gesagt, brauche ich mehr Details zu den Kosten. 
+Könnten wir dazu vielleicht nächste Woche einen kurzen Termin ausmachen? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No entiendo el plan del todo. ¿Podría explicarlo más detalladamente? A primera vista suena bien, pero como ya he dicho, necesito más detalles sobre los costes. ¿Podríamos quizás fijar una breve reunión la semana que viene para tratar esto? </t>
+  </si>
+  <si>
+    <t>Chunks_20</t>
+  </si>
+  <si>
+    <t>Hacer planes</t>
+  </si>
+  <si>
+    <t>Passt das für dich?" / "Geht das klar?": "¿te hace?" o "¿te cuadra?". 
+"Ich trage es mir ein" / "Machen wir so!" --&gt; "Quedamos así"
+📅 A distancia / Plan futuro: "¡Nos vemos a las ocho! Ich freu mich!" (= ¡Qué ganas!).
+Abreviatura de Es freut mich, Sie/dich kennenzulernen
+🤝 Cara a cara / Primera vez: "Hola, soy [Tu Nombre]. Freut mich!" (= Encantado).</t>
+  </si>
+  <si>
+    <t>¿Te apetece una pizza esta noche?
+A mí me da igual, lo que a ti te apetezca / de lo que tengas hambre.
+¿A qué hora quedamos?
+Pongamos que a las ocho delante del restaurante, ¿te hace? / ¿te va bien?
+¡Perfecto, quedamos así! Me lo apunto en la agenda / Nos vemos allí.</t>
+  </si>
+  <si>
+    <t>Hast du Lust auf Pizza heute Abend?
+Mir ist es egal, worauf du Hunger hast.
+Wann treffen wir uns?
+Sagen wir mal um acht vor dem Restaurant, geht das klar?
+Perfekt, dann sehen wir uns da. Ich freu mich!</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
@@ -1657,392 +1745,454 @@
       </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+    <row r="23" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+    <row r="25" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+    <row r="26" spans="1:6" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+    <row r="27" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="143.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+    <row r="28" spans="1:6" ht="143.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+    <row r="29" spans="1:6" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="58.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="58.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="208" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="208" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="208.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="273.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="208" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="208" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="208.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="234.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="273.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="286.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="4"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="4"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="4"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="4"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="4"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
@@ -2076,31 +2226,31 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
-      <c r="B48" s="1"/>
+      <c r="B48" s="6"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
-      <c r="B49" s="1"/>
+      <c r="B49" s="6"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
-      <c r="B50" s="1"/>
+      <c r="B50" s="6"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
-      <c r="B51" s="1"/>
+      <c r="B51" s="6"/>
       <c r="C51" s="3"/>
       <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
-      <c r="B52" s="1"/>
+      <c r="B52" s="6"/>
       <c r="C52" s="3"/>
       <c r="D52" s="4"/>
     </row>
@@ -2115,6 +2265,36 @@
       <c r="B54" s="1"/>
       <c r="C54" s="3"/>
       <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="4"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="4"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="4"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="4"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="4"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
